--- a/entrega/tabla-stride-cliente.xlsx
+++ b/entrega/tabla-stride-cliente.xlsx
@@ -8,6 +8,7 @@
   </bookViews>
   <sheets>
     <sheet name="STRIDE_Cliente" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Priorizacion" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -33,7 +34,7 @@
       <b val="1"/>
     </font>
   </fonts>
-  <fills count="6">
+  <fills count="5">
     <fill>
       <patternFill/>
     </fill>
@@ -43,24 +44,16 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="0008427B"/>
-        <bgColor rgb="0008427B"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00FFC7CE"/>
-        <bgColor rgb="00FFC7CE"/>
+        <fgColor rgb="00F4CCCC"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00FFEB9C"/>
-        <bgColor rgb="00FFEB9C"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00C6EFCE"/>
+        <fgColor rgb="00FFF2CC"/>
       </patternFill>
     </fill>
   </fills>
@@ -74,26 +67,26 @@
     </border>
     <border>
       <left style="thin">
-        <color rgb="00CCCCCC"/>
+        <color rgb="00BFBFBF"/>
       </left>
       <right style="thin">
-        <color rgb="00CCCCCC"/>
+        <color rgb="00BFBFBF"/>
       </right>
       <top style="thin">
-        <color rgb="00CCCCCC"/>
+        <color rgb="00BFBFBF"/>
       </top>
       <bottom style="thin">
-        <color rgb="00CCCCCC"/>
+        <color rgb="00BFBFBF"/>
       </bottom>
     </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
@@ -102,9 +95,6 @@
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -472,21 +462,21 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L8"/>
+  <dimension ref="A1:L9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
-    <col width="26" customWidth="1" min="2" max="2"/>
-    <col width="16" customWidth="1" min="3" max="3"/>
-    <col width="42" customWidth="1" min="4" max="4"/>
-    <col width="42" customWidth="1" min="5" max="5"/>
-    <col width="28" customWidth="1" min="6" max="6"/>
+    <col width="30" customWidth="1" min="2" max="2"/>
+    <col width="18" customWidth="1" min="3" max="3"/>
+    <col width="44" customWidth="1" min="4" max="4"/>
+    <col width="44" customWidth="1" min="5" max="5"/>
+    <col width="30" customWidth="1" min="6" max="6"/>
     <col width="12" customWidth="1" min="7" max="7"/>
     <col width="12" customWidth="1" min="8" max="8"/>
-    <col width="32" customWidth="1" min="9" max="9"/>
-    <col width="34" customWidth="1" min="10" max="10"/>
-    <col width="22" customWidth="1" min="11" max="11"/>
-    <col width="14" customWidth="1" min="12" max="12"/>
+    <col width="36" customWidth="1" min="9" max="9"/>
+    <col width="38" customWidth="1" min="10" max="10"/>
+    <col width="24" customWidth="1" min="11" max="11"/>
+    <col width="12" customWidth="1" min="12" max="12"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -551,7 +541,7 @@
         </is>
       </c>
     </row>
-    <row r="2" ht="70" customHeight="1">
+    <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
           <t>T1</t>
@@ -559,7 +549,7 @@
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>Repositorio de Programación (SharePoint Lists/Excel)</t>
+          <t>D2 Hoja de Muestreo y D3 Hoja de Asignación PAT (Excel en OneDrive) · origen: H2, H3</t>
         </is>
       </c>
       <c r="C2" s="2" t="inlineStr">
@@ -569,17 +559,17 @@
       </c>
       <c r="D2" s="2" t="inlineStr">
         <is>
-          <t>Exposición de datos personales de estudiantes y profesores (correos, horarios, respuestas) por permisos de uso compartido demasiado amplios.</t>
+          <t>Los datos personales copiados de SIGA (nombres, correos, programas, horarios) quedan expuestos si las hojas se comparten con más personas de las necesarias o con enlaces amplios ("Cualquier persona" o "Personas de la organización").</t>
         </is>
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>Un enlace de tipo "cualquiera con el vínculo" a la lista/Excel se comparte o reenvía accidentalmente, exponiendo datos personales de estudiantes fuera del equipo del proyecto.</t>
+          <t>La coordinadora comparte la Hoja de Asignación PAT con un enlace de "Personas de la organización" para que los PAT registren su disponibilidad; el enlace se reenvía y cualquier usuario de la universidad puede abrir la hoja con los datos de toda la muestra.</t>
         </is>
       </c>
       <c r="F2" s="2" t="inlineStr">
         <is>
-          <t>Alto - incumplimiento de la Ley 1581 de 2012 (Habeas Data) y de la política de protección de datos de la Universidad de La Sabana</t>
+          <t>Alto - exposición de datos personales; incumplimiento del principio de acceso y circulación restringida (Ley 1581 de 2012) y de la política de datos de la universidad</t>
         </is>
       </c>
       <c r="G2" s="2" t="inlineStr">
@@ -594,17 +584,17 @@
       </c>
       <c r="I2" s="2" t="inlineStr">
         <is>
-          <t>Permisos por defecto del tenant institucional de Microsoft 365; no se confirmó restricción explícita del sitio de SharePoint al equipo autorizado.</t>
+          <t>Las hojas están en el OneDrive de la cuenta institucional de la coordinadora (confirmado). No se confirmó con quién se comparten ni con qué tipo de enlace (pregunta P2), ni si el tenant bloquea los enlaces "Cualquier persona".</t>
         </is>
       </c>
       <c r="J2" s="2" t="inlineStr">
         <is>
-          <t>Restringir el sitio de SharePoint solo a los roles autorizados, deshabilitar enlaces "cualquiera con el vínculo" para datos de estudiantes, y aplicar etiquetas de sensibilidad (Microsoft Purview Information Protection).</t>
+          <t>Compartir solo con personas específicas y con permiso de lectura cuando no se necesite edición; revisar "Administrar acceso" de cada hoja; separar la disponibilidad de los PAT en un archivo sin datos de terceros; pedir a TI que confirme la política de enlaces del tenant.</t>
         </is>
       </c>
       <c r="K2" s="2" t="inlineStr">
         <is>
-          <t>Equipo de Arquitectura / TI Universidad</t>
+          <t>Coordinadora de la encuesta / Dirección de TI</t>
         </is>
       </c>
       <c r="L2" s="2" t="inlineStr">
@@ -613,7 +603,7 @@
         </is>
       </c>
     </row>
-    <row r="3" ht="70" customHeight="1">
+    <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
           <t>T2</t>
@@ -621,7 +611,7 @@
       </c>
       <c r="B3" s="2" t="inlineStr">
         <is>
-          <t>Panel de Coordinación (Excel/Power BI) - Autenticación del Coordinador</t>
+          <t>Cuenta institucional de la coordinadora (E2): acceso a SIGA, OneDrive y Exchange · origen: H6, H2</t>
         </is>
       </c>
       <c r="C3" s="2" t="inlineStr">
@@ -631,17 +621,17 @@
       </c>
       <c r="D3" s="2" t="inlineStr">
         <is>
-          <t>Un atacante se hace pasar por la coordinadora de encuestas usando credenciales robadas o phishing para acceder al panel y alterar criterios de la encuesta.</t>
+          <t>Un atacante se hace pasar por la coordinadora con credenciales robadas. Como una sola cuenta concentra el acceso a SIGA, a las dos hojas y al buzón, el robo de esa cuenta compromete todo el proceso.</t>
         </is>
       </c>
       <c r="E3" s="2" t="inlineStr">
         <is>
-          <t>Atacante obtiene credenciales institucionales de la coordinadora mediante phishing dirigido y accede al panel de coordinación para modificar fecha, capacidad o criterios de muestra.</t>
+          <t>En la temporada de la encuesta llega un correo de phishing que imita un aviso de Microsoft 365; la coordinadora ingresa su contraseña y, si no hay MFA, el atacante descarga las hojas con los datos de la muestra y lee las respuestas de los profesores.</t>
         </is>
       </c>
       <c r="F3" s="2" t="inlineStr">
         <is>
-          <t>Alto - manipulación de la logística oficial de la encuesta institucional</t>
+          <t>Alto - acceso no autorizado a datos personales y a la programación oficial de la encuesta</t>
         </is>
       </c>
       <c r="G3" s="2" t="inlineStr">
@@ -656,17 +646,17 @@
       </c>
       <c r="I3" s="2" t="inlineStr">
         <is>
-          <t>Autenticación corporativa Microsoft 365 / Azure AD; no se confirmó que el MFA (autenticación multifactor) sea obligatorio para esta cuenta.</t>
+          <t>Autenticación de Microsoft 365 (Entra ID) con la cuenta institucional. No se confirmó si el MFA es obligatorio para esta cuenta (pregunta P3).</t>
         </is>
       </c>
       <c r="J3" s="2" t="inlineStr">
         <is>
-          <t>Exigir MFA obligatorio y Conditional Access (bloqueo por ubicación/dispositivo no confiable) para todas las cuentas con acceso al panel de coordinación.</t>
+          <t>Exigir MFA en la cuenta de la coordinadora; acceso condicional si TI lo tiene disponible; recordatorio de phishing antes del periodo de la encuesta.</t>
         </is>
       </c>
       <c r="K3" s="2" t="inlineStr">
         <is>
-          <t>Equipo de Seguridad / TI Universidad</t>
+          <t>Dirección de TI</t>
         </is>
       </c>
       <c r="L3" s="2" t="inlineStr">
@@ -675,7 +665,7 @@
         </is>
       </c>
     </row>
-    <row r="4" ht="70" customHeight="1">
+    <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
           <t>T3</t>
@@ -683,305 +673,661 @@
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>Flujo de Cruce de Horarios y Repositorio de Programación</t>
+          <t>D1 Archivos exportados de SIGA (CSV/Excel en el equipo de la coordinadora) · origen: H2</t>
         </is>
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>Information Disclosure</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>Las exportaciones de SIGA se descargan al equipo local y quedan ahí después de cargarlas a las hojas. Si el equipo se pierde, se comparte o se sincroniza con otra nube, los datos quedan expuestos sin ningún control de SIGA.</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>El portátil de la coordinadora se pierde fuera de la universidad; la carpeta de descargas tiene exportaciones de SIGA de varios años con nombres, correos y horarios de estudiantes y profesores.</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>Alto - exposición de datos personales acumulados de varias encuestas</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>Media</t>
+        </is>
+      </c>
+      <c r="H4" s="3" t="inlineStr">
+        <is>
+          <t>Alto</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>Ninguno documentado. No se confirmó si el disco del equipo está cifrado ni si los archivos se borran al terminar la encuesta (pregunta P4).</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
+          <t>Borrar las exportaciones apenas se carguen a las hojas; si deben guardarse, moverlas a OneDrive con acceso restringido; confirmar con TI el cifrado del disco (BitLocker).</t>
+        </is>
+      </c>
+      <c r="K4" s="2" t="inlineStr">
+        <is>
+          <t>Coordinadora de la encuesta / Dirección de TI</t>
+        </is>
+      </c>
+      <c r="L4" s="2" t="inlineStr">
+        <is>
+          <t>Pendiente</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="2" t="inlineStr">
+        <is>
+          <t>T4</t>
+        </is>
+      </c>
+      <c r="B5" s="2" t="inlineStr">
+        <is>
+          <t>Procesos P1-P4 (operación manual) y equipo de la coordinadora · origen: H6, H3</t>
+        </is>
+      </c>
+      <c r="C5" s="2" t="inlineStr">
+        <is>
+          <t>Denial of Service</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>El proceso se detiene si la única persona que lo opera no está disponible, si su cuenta se bloquea, si su equipo falla o si una de las hojas se borra o se corrompe.</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>La coordinadora se incapacita la semana en que hay que avisar a los profesores; nadie más conoce el procedimiento ni tiene acceso a las hojas, y la aplicación de la encuesta se aplaza.</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>Alto - retraso o pérdida del ciclo anual de la encuesta, que es insumo de la autoevaluación institucional</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>Media</t>
+        </is>
+      </c>
+      <c r="H5" s="3" t="inlineStr">
+        <is>
+          <t>Alto</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>OneDrive conserva los archivos eliminados en la papelera de reciclaje por un tiempo limitado (función por defecto del servicio). No hay procedimiento documentado ni una segunda persona con acceso.</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
+          <t>Documentar el procedimiento paso a paso; designar una persona de respaldo con acceso a las hojas; mover las hojas del OneDrive personal a un sitio de SharePoint del área.</t>
+        </is>
+      </c>
+      <c r="K5" s="2" t="inlineStr">
+        <is>
+          <t>Vicerrectoría de Desarrollo</t>
+        </is>
+      </c>
+      <c r="L5" s="2" t="inlineStr">
+        <is>
+          <t>Pendiente</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="2" t="inlineStr">
+        <is>
+          <t>T5</t>
+        </is>
+      </c>
+      <c r="B6" s="2" t="inlineStr">
+        <is>
+          <t>D3 Hoja de Asignación PAT y flujo F6 (copia manual desde D2) · origen: H3, H4</t>
+        </is>
+      </c>
+      <c r="C6" s="2" t="inlineStr">
+        <is>
+          <t>Tampering</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>Una modificación accidental o no autorizada de la hoja (sobrescribir celdas, ordenar mal una columna, borrar filas) cambia qué clases se notifican, sin que nadie lo detecte.</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>Al ordenar la columna de horarios sin seleccionar todo el rango, la disponibilidad de los PAT queda cruzada con clases equivocadas y se avisa a profesores que no estaban en la muestra.</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>Medio - avisos equivocados, reprocesos y pérdida de confianza de los profesores</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>Media</t>
+        </is>
+      </c>
+      <c r="H6" s="4" t="inlineStr">
+        <is>
+          <t>Medio</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>Historial de versiones de OneDrive (función por defecto; no se confirmó que se use para revisar cambios). Sin celdas protegidas ni validación de datos.</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
+          <t>Proteger las columnas calculadas y los rangos fijos; usar validación de datos (listas desplegables de clases y horarios); revisar la asignación antes de enviar los avisos.</t>
+        </is>
+      </c>
+      <c r="K6" s="2" t="inlineStr">
+        <is>
+          <t>Coordinadora de la encuesta</t>
+        </is>
+      </c>
+      <c r="L6" s="2" t="inlineStr">
+        <is>
+          <t>Pendiente</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="2" t="inlineStr">
+        <is>
+          <t>T6</t>
+        </is>
+      </c>
+      <c r="B7" s="2" t="inlineStr">
+        <is>
+          <t>D4 Buzón de la coordinadora (Exchange Online) y flujo F11 (respuesta del profesor) · origen: H5</t>
+        </is>
+      </c>
+      <c r="C7" s="2" t="inlineStr">
+        <is>
           <t>Repudiation</t>
         </is>
       </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>Las respuestas de los profesores quedan dispersas en el buzón y no se registran en la hoja. Un profesor puede negar que aceptó (o que recibió el aviso) y no hay un registro rápido que lo demuestre.</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>Un profesor afirma que nunca aceptó ceder su clase y no deja entrar al PAT; la respuesta está en un hilo de correo que nadie registró en la Hoja de Asignación PAT.</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>Medio - conflictos con profesores y clases perdidas para la muestra</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>Media</t>
+        </is>
+      </c>
+      <c r="H7" s="4" t="inlineStr">
+        <is>
+          <t>Medio</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>Los correos enviados y recibidos quedan en Exchange Online (evidencia dispersa, no estructurada). No se confirmó si el registro de auditoría de Microsoft Purview está activo (pregunta P5).</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
+          <t>Registrar cada respuesta en la Hoja de Asignación PAT (fecha, profesor, decisión, enlace al correo); usar una carpeta o categoría de Outlook para las respuestas de la encuesta.</t>
+        </is>
+      </c>
+      <c r="K7" s="2" t="inlineStr">
+        <is>
+          <t>Coordinadora de la encuesta</t>
+        </is>
+      </c>
+      <c r="L7" s="2" t="inlineStr">
+        <is>
+          <t>Pendiente</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="2" t="inlineStr">
+        <is>
+          <t>T7</t>
+        </is>
+      </c>
+      <c r="B8" s="2" t="inlineStr">
+        <is>
+          <t>Flujo F1 (exportación de SIGA) hacia D1, D2 y D3 · origen: H1, H2</t>
+        </is>
+      </c>
+      <c r="C8" s="2" t="inlineStr">
+        <is>
+          <t>Elevation of Privilege</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>La exportación trae todos los campos que la coordinadora puede ver en SIGA. Una vez en Excel, cualquier persona con acceso a la hoja obtiene datos que su propio rol en SIGA no le permitiría consultar: el control de acceso de SIGA deja de aplicar.</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>Un estudiante PAT con permiso de edición en la Hoja de Asignación PAT ve los correos y horarios de toda la muestra y de los profesores, información a la que no tiene acceso en SIGA.</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>Alto - acceso a datos personales sin pasar por los controles de SIGA</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>Baja</t>
+        </is>
+      </c>
+      <c r="H8" s="4" t="inlineStr">
+        <is>
+          <t>Medio</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>Control de acceso por rol dentro de SIGA (fuera del alcance de la Vicerrectoría). Ningún control sobre las copias exportadas.</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
+          <t>Exportar solo las columnas necesarias para la muestra y la asignación (minimización); no dar acceso a las hojas a personas sin el rol de la coordinadora.</t>
+        </is>
+      </c>
+      <c r="K8" s="2" t="inlineStr">
+        <is>
+          <t>Coordinadora de la encuesta / Dirección de TI</t>
+        </is>
+      </c>
+      <c r="L8" s="2" t="inlineStr">
+        <is>
+          <t>Pendiente</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="2" t="inlineStr">
+        <is>
+          <t>T8</t>
+        </is>
+      </c>
+      <c r="B9" s="2" t="inlineStr">
+        <is>
+          <t>Flujo F10 (aviso a profesores por correo, uno a uno) · origen: H5, H2</t>
+        </is>
+      </c>
+      <c r="C9" s="2" t="inlineStr">
+        <is>
+          <t>Information Disclosure</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>Al escribir cada correo a mano, el autocompletado de Outlook o una lista copiada mal pueden enviar el aviso, con datos de la clase, al destinatario equivocado.</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>La coordinadora escribe el apellido del profesor y Outlook autocompleta otra persona; el aviso con el curso, el horario y el salón llega a alguien ajeno al proceso.</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>Medio - exposición de datos de la clase; sube a Alto si el correo incluye datos de estudiantes (no confirmado)</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>Media</t>
+        </is>
+      </c>
+      <c r="H9" s="4" t="inlineStr">
+        <is>
+          <t>Medio</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>Correo institucional autenticado (Exchange Online); los correos enviados quedan en Elementos enviados. Sin revisión de destinatarios.</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
+          <t>Plantilla de aviso sin datos de estudiantes; tomar el correo del profesor de la hoja, no del autocompletado; revisar destinatarios antes de enviar.</t>
+        </is>
+      </c>
+      <c r="K9" s="2" t="inlineStr">
+        <is>
+          <t>Coordinadora de la encuesta</t>
+        </is>
+      </c>
+      <c r="L9" s="2" t="inlineStr">
+        <is>
+          <t>Pendiente</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:F9"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="10" customWidth="1" min="1" max="1"/>
+    <col width="6" customWidth="1" min="2" max="2"/>
+    <col width="22" customWidth="1" min="3" max="3"/>
+    <col width="60" customWidth="1" min="4" max="4"/>
+    <col width="14" customWidth="1" min="5" max="5"/>
+    <col width="18" customWidth="1" min="6" max="6"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Prioridad</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>ID</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>Tipo STRIDE</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>Componente / Activo</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>Nivel de Riesgo</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>Hallazgo de origen (Taller 4)</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="B2" s="2" t="inlineStr">
+        <is>
+          <t>T1</t>
+        </is>
+      </c>
+      <c r="C2" s="2" t="inlineStr">
+        <is>
+          <t>Information Disclosure</t>
+        </is>
+      </c>
+      <c r="D2" s="2" t="inlineStr">
+        <is>
+          <t>D2 Hoja de Muestreo y D3 Hoja de Asignación PAT (Excel en OneDrive)</t>
+        </is>
+      </c>
+      <c r="E2" s="3" t="inlineStr">
+        <is>
+          <t>Alto</t>
+        </is>
+      </c>
+      <c r="F2" s="2" t="inlineStr">
+        <is>
+          <t>H2, H3</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="B3" s="2" t="inlineStr">
+        <is>
+          <t>T2</t>
+        </is>
+      </c>
+      <c r="C3" s="2" t="inlineStr">
+        <is>
+          <t>Spoofing</t>
+        </is>
+      </c>
+      <c r="D3" s="2" t="inlineStr">
+        <is>
+          <t>Cuenta institucional de la coordinadora (E2): acceso a SIGA, OneDrive y Exchange</t>
+        </is>
+      </c>
+      <c r="E3" s="3" t="inlineStr">
+        <is>
+          <t>Alto</t>
+        </is>
+      </c>
+      <c r="F3" s="2" t="inlineStr">
+        <is>
+          <t>H6, H2</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="B4" s="2" t="inlineStr">
+        <is>
+          <t>T3</t>
+        </is>
+      </c>
+      <c r="C4" s="2" t="inlineStr">
+        <is>
+          <t>Information Disclosure</t>
+        </is>
+      </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>Falta de registro de auditoría que permita rastrear qué criterios se aplicaron y quién los definió, dificultando resolver disputas sobre por qué un programa o grupo fue excluido de la muestra.</t>
-        </is>
-      </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>Un programa académico cuestiona por qué no fue incluido en la muestra significativa y no existe un registro con marca de tiempo, usuario y criterios exactos usados en esa ejecución del flujo.</t>
+          <t>D1 Archivos exportados de SIGA (CSV/Excel en el equipo de la coordinadora)</t>
+        </is>
+      </c>
+      <c r="E4" s="3" t="inlineStr">
+        <is>
+          <t>Alto</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>Medio - dificulta resolver disputas y auditar el cumplimiento de la muestra significativa</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>Media</t>
-        </is>
-      </c>
-      <c r="H4" s="4" t="inlineStr">
+          <t>H2</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="2" t="n">
+        <v>4</v>
+      </c>
+      <c r="B5" s="2" t="inlineStr">
+        <is>
+          <t>T4</t>
+        </is>
+      </c>
+      <c r="C5" s="2" t="inlineStr">
+        <is>
+          <t>Denial of Service</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>Procesos P1-P4 (operación manual) y equipo de la coordinadora</t>
+        </is>
+      </c>
+      <c r="E5" s="3" t="inlineStr">
+        <is>
+          <t>Alto</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>H6, H3</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="B6" s="2" t="inlineStr">
+        <is>
+          <t>T5</t>
+        </is>
+      </c>
+      <c r="C6" s="2" t="inlineStr">
+        <is>
+          <t>Tampering</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>D3 Hoja de Asignación PAT y flujo F6 (copia manual desde D2)</t>
+        </is>
+      </c>
+      <c r="E6" s="4" t="inlineStr">
         <is>
           <t>Medio</t>
         </is>
       </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>Historial de versiones básico de SharePoint/Excel; sin logs de auditoría explícitos vinculados a cada ejecución (run) del flujo de Power Automate.</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>Activar y retener el historial de ejecuciones (run history) de cada flujo de Power Automate y habilitar logs de auditoría de Microsoft Purview para acciones sensibles.</t>
-        </is>
-      </c>
-      <c r="K4" s="2" t="inlineStr">
-        <is>
-          <t>Equipo de Automatización</t>
-        </is>
-      </c>
-      <c r="L4" s="2" t="inlineStr">
-        <is>
-          <t>Pendiente</t>
-        </is>
-      </c>
-    </row>
-    <row r="5" ht="70" customHeight="1">
-      <c r="A5" s="2" t="inlineStr">
-        <is>
-          <t>T4</t>
-        </is>
-      </c>
-      <c r="B5" s="2" t="inlineStr">
-        <is>
-          <t>Flujo de Cruce de Horarios - Dependencia de SIGA</t>
-        </is>
-      </c>
-      <c r="C5" s="2" t="inlineStr">
-        <is>
-          <t>Denial of Service</t>
-        </is>
-      </c>
-      <c r="D5" s="2" t="inlineStr">
-        <is>
-          <t>Si SIGA no responde o se alcanza el límite de solicitudes (throttling) del conector, el flujo de cruce de horarios falla y detiene toda la programación de la encuesta.</t>
-        </is>
-      </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>Durante la ejecución masiva de consultas a SIGA en la semana de cruce de horarios, se alcanza el límite de solicitudes del conector y el flujo falla sin que nadie lo note a tiempo.</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>Medio - retraso o incumplimiento del cronograma de aplicación de la encuesta institucional</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
-        <is>
-          <t>Media</t>
-        </is>
-      </c>
-      <c r="H5" s="4" t="inlineStr">
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>H3, H4</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="2" t="n">
+        <v>6</v>
+      </c>
+      <c r="B7" s="2" t="inlineStr">
+        <is>
+          <t>T6</t>
+        </is>
+      </c>
+      <c r="C7" s="2" t="inlineStr">
+        <is>
+          <t>Repudiation</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>D4 Buzón de la coordinadora (Exchange Online) y flujo F11 (respuesta del profesor)</t>
+        </is>
+      </c>
+      <c r="E7" s="4" t="inlineStr">
         <is>
           <t>Medio</t>
         </is>
       </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>Reintentos automáticos básicos de Power Automate; sin monitoreo proactivo de fallos ni alertas configuradas.</t>
-        </is>
-      </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>Configurar alertas de fallo de flujo, política de reintentos con backoff exponencial, y un procedimiento manual de contingencia si SIGA no está disponible.</t>
-        </is>
-      </c>
-      <c r="K5" s="2" t="inlineStr">
-        <is>
-          <t>Equipo de Automatización / TI Universidad</t>
-        </is>
-      </c>
-      <c r="L5" s="2" t="inlineStr">
-        <is>
-          <t>Pendiente</t>
-        </is>
-      </c>
-    </row>
-    <row r="6" ht="70" customHeight="1">
-      <c r="A6" s="2" t="inlineStr">
-        <is>
-          <t>T5</t>
-        </is>
-      </c>
-      <c r="B6" s="2" t="inlineStr">
-        <is>
-          <t>Cuenta de conexión del Flujo de Power Automate</t>
-        </is>
-      </c>
-      <c r="C6" s="2" t="inlineStr">
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>H5</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="2" t="n">
+        <v>7</v>
+      </c>
+      <c r="B8" s="2" t="inlineStr">
+        <is>
+          <t>T7</t>
+        </is>
+      </c>
+      <c r="C8" s="2" t="inlineStr">
         <is>
           <t>Elevation of Privilege</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
-        <is>
-          <t>Los flujos se ejecutan con la identidad de una cuenta de conexión; si esa cuenta tiene permisos más amplios de los necesarios, cualquiera con acceso de edición al flujo podría usarlos para leer o modificar datos fuera del alcance del proyecto.</t>
-        </is>
-      </c>
-      <c r="E6" s="2" t="inlineStr">
-        <is>
-          <t>Un colaborador con acceso de edición al flujo agrega una acción que consulta otra lista de SharePoint a la que la cuenta de servicio tiene acceso, fuera del alcance autorizado del proyecto de encuestas.</t>
-        </is>
-      </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>Alto - acceso no autorizado a otros datos institucionales mediante una cuenta con privilegios excesivos</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>Baja</t>
-        </is>
-      </c>
-      <c r="H6" s="4" t="inlineStr">
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>Flujo F1 (exportación de SIGA) hacia D1, D2 y D3</t>
+        </is>
+      </c>
+      <c r="E8" s="4" t="inlineStr">
         <is>
           <t>Medio</t>
         </is>
       </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>Cuenta de conexión compartida del equipo; no se confirmó la aplicación del principio de mínimo privilegio.</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>Aplicar mínimo privilegio a la cuenta de conexión del flujo y usar un entorno (environment) de Power Platform separado con políticas DLP que restrinjan conectores.</t>
-        </is>
-      </c>
-      <c r="K6" s="2" t="inlineStr">
-        <is>
-          <t>Equipo de Automatización / TI Universidad</t>
-        </is>
-      </c>
-      <c r="L6" s="2" t="inlineStr">
-        <is>
-          <t>En análisis</t>
-        </is>
-      </c>
-    </row>
-    <row r="7" ht="70" customHeight="1">
-      <c r="A7" s="2" t="inlineStr">
-        <is>
-          <t>T6</t>
-        </is>
-      </c>
-      <c r="B7" s="2" t="inlineStr">
-        <is>
-          <t>Flujo de Notificación a Profesores - Respuesta de Aceptación</t>
-        </is>
-      </c>
-      <c r="C7" s="2" t="inlineStr">
-        <is>
-          <t>Tampering</t>
-        </is>
-      </c>
-      <c r="D7" s="2" t="inlineStr">
-        <is>
-          <t>La respuesta de aceptación/rechazo del profesor podría ser interceptada o falsificada, forzando la aceptación de la cesión del espacio sin su consentimiento real.</t>
-        </is>
-      </c>
-      <c r="E7" s="2" t="inlineStr">
-        <is>
-          <t>El enlace o formulario de aceptación es reenviado o manipulado, permitiendo que alguien distinto al profesor confirme la cesión del espacio de clase.</t>
-        </is>
-      </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>Medio - se programa la encuesta en un espacio sin autorización real del docente</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
-        <is>
-          <t>Baja</t>
-        </is>
-      </c>
-      <c r="H7" s="5" t="inlineStr">
-        <is>
-          <t>Bajo</t>
-        </is>
-      </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>Enlaces de aprobación de Power Automate; no se confirmó que exijan token de un solo uso con expiración corta ni verificación de identidad Azure AD.</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>Usar tokens de aprobación de un solo uso con expiración corta y exigir inicio de sesión institucional (Azure AD) para confirmar la respuesta.</t>
-        </is>
-      </c>
-      <c r="K7" s="2" t="inlineStr">
-        <is>
-          <t>Equipo de Automatización</t>
-        </is>
-      </c>
-      <c r="L7" s="2" t="inlineStr">
-        <is>
-          <t>En análisis</t>
-        </is>
-      </c>
-    </row>
-    <row r="8" ht="70" customHeight="1">
-      <c r="A8" s="2" t="inlineStr">
-        <is>
-          <t>T7</t>
-        </is>
-      </c>
-      <c r="B8" s="2" t="inlineStr">
-        <is>
-          <t>Correo institucional - Enlace de la encuesta (Microsoft Forms)</t>
-        </is>
-      </c>
-      <c r="C8" s="2" t="inlineStr">
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>H1, H2</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="2" t="n">
+        <v>8</v>
+      </c>
+      <c r="B9" s="2" t="inlineStr">
+        <is>
+          <t>T8</t>
+        </is>
+      </c>
+      <c r="C9" s="2" t="inlineStr">
         <is>
           <t>Information Disclosure</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
-        <is>
-          <t>El enlace de la encuesta, si no exige autenticación adicional, puede ser reenviado fuera de la muestra seleccionada, permitiendo respuestas de estudiantes no autorizados.</t>
-        </is>
-      </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>Un estudiante de la muestra reenvía su enlace de encuesta a un compañero fuera de la muestra significativa, invalidando la representatividad de los resultados.</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>Bajo-Medio - afecta la validez estadística de la muestra, no expone datos sensibles adicionales</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>Media</t>
-        </is>
-      </c>
-      <c r="H8" s="5" t="inlineStr">
-        <is>
-          <t>Bajo</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>Enlace único generado por Microsoft Forms; no se confirmó restricción de "solo usuarios de la organización" ni límite de una respuesta por usuario.</t>
-        </is>
-      </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>Configurar Microsoft Forms para restringir las respuestas a usuarios autenticados de la organización y limitar una respuesta por persona.</t>
-        </is>
-      </c>
-      <c r="K8" s="2" t="inlineStr">
-        <is>
-          <t>Equipo de Automatización</t>
-        </is>
-      </c>
-      <c r="L8" s="2" t="inlineStr">
-        <is>
-          <t>Pendiente</t>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>Flujo F10 (aviso a profesores por correo, uno a uno)</t>
+        </is>
+      </c>
+      <c r="E9" s="4" t="inlineStr">
+        <is>
+          <t>Medio</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>H5, H2</t>
         </is>
       </c>
     </row>
